--- a/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_SHEEP_DESERT_RAM.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/XLXS/2026_SHEEP_DESERT_RAM.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,8 +65,19 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002F1B0F"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -103,8 +114,28 @@
         <fgColor rgb="004F2D1D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE3D3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B301B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F1E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFE5D7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -140,11 +171,25 @@
         <color rgb="00B8895F"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C58F61"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C58F61"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C58F61"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C58F61"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -190,6 +235,45 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -582,1663 +666,1663 @@
   <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" min="13" max="13"/>
-    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
         <is>
           <t>2026 SHEEP DESERT RAM</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1"/>
+    <row r="2" ht="40" customHeight="1"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>Hunt Name</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="20" t="inlineStr">
         <is>
           <t>Hunt Code</t>
         </is>
       </c>
-      <c r="C3" s="9" t="inlineStr">
+      <c r="C3" s="20" t="inlineStr">
         <is>
           <t>Sex</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="D3" s="20" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="20" t="inlineStr">
         <is>
           <t>Weapon</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
         <is>
           <t>Hunt Type</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="G3" s="20" t="inlineStr">
         <is>
           <t>Season</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="20" t="inlineStr">
         <is>
           <t>Res</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="20" t="inlineStr">
         <is>
           <t>Non-Res</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="J3" s="20" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="20" t="inlineStr">
         <is>
           <t>Harvest Prior Year</t>
         </is>
       </c>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="20" t="inlineStr">
         <is>
           <t>Percent Harvest Success (previous hunting season)</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t>Average Age Harvested (previous hunting season)</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="N3" s="20" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>Desert Bighorn Sheep - Statewide Permit</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>DS1000</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D4" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
+      <c r="F4" s="25" t="inlineStr">
         <is>
           <t>Statewide</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t>Sept 1 - Dec 31, 2026</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr"/>
-      <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="13" t="inlineStr"/>
-      <c r="K4" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="H4" s="26" t="inlineStr"/>
+      <c r="I4" s="26" t="inlineStr"/>
+      <c r="J4" s="26" t="inlineStr"/>
+      <c r="K4" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L4" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr"/>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="M4" s="26" t="inlineStr"/>
+      <c r="N4" s="26" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>Kaiparowits, East</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>DS1002</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="27" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H5" s="15" t="inlineStr"/>
-      <c r="I5" s="15" t="inlineStr"/>
-      <c r="J5" s="15" t="inlineStr"/>
-      <c r="K5" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L5" s="14" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr"/>
+      <c r="I5" s="28" t="inlineStr"/>
+      <c r="J5" s="28" t="inlineStr"/>
+      <c r="K5" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L5" s="28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M5" s="14" t="inlineStr"/>
-      <c r="N5" s="14" t="inlineStr">
+      <c r="M5" s="28" t="inlineStr"/>
+      <c r="N5" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Kaiparowits, Escalante East/West</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>DS1003</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F6" s="13" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>Sept 12 - Nov 10, 2026</t>
         </is>
       </c>
-      <c r="H6" s="13" t="inlineStr"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr"/>
-      <c r="K6" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L6" s="14" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr"/>
+      <c r="I6" s="26" t="inlineStr"/>
+      <c r="J6" s="26" t="inlineStr"/>
+      <c r="K6" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M6" s="14" t="inlineStr"/>
-      <c r="N6" s="14" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr"/>
+      <c r="N6" s="26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>San Rafael, Dirty Devil</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>DS1004</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G7" s="15" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>Sept 13 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H7" s="15" t="inlineStr"/>
-      <c r="I7" s="15" t="inlineStr"/>
-      <c r="J7" s="15" t="inlineStr"/>
-      <c r="K7" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L7" s="14" t="inlineStr">
+      <c r="H7" s="28" t="inlineStr"/>
+      <c r="I7" s="28" t="inlineStr"/>
+      <c r="J7" s="28" t="inlineStr"/>
+      <c r="K7" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L7" s="28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M7" s="14" t="inlineStr"/>
-      <c r="N7" s="14" t="inlineStr">
+      <c r="M7" s="28" t="inlineStr"/>
+      <c r="N7" s="28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Kaiparowits, West</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>DS1006</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F8" s="13" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H8" s="13" t="inlineStr"/>
-      <c r="I8" s="13" t="inlineStr"/>
-      <c r="J8" s="13" t="inlineStr"/>
-      <c r="K8" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="H8" s="26" t="inlineStr"/>
+      <c r="I8" s="26" t="inlineStr"/>
+      <c r="J8" s="26" t="inlineStr"/>
+      <c r="K8" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M8" s="14" t="inlineStr"/>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="M8" s="26" t="inlineStr"/>
+      <c r="N8" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="27" t="inlineStr">
         <is>
           <t>San Rafael, South</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>DS1007</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="F9" s="27" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G9" s="15" t="inlineStr">
+      <c r="G9" s="27" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H9" s="15" t="inlineStr"/>
-      <c r="I9" s="15" t="inlineStr"/>
-      <c r="J9" s="15" t="inlineStr"/>
-      <c r="K9" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="H9" s="28" t="inlineStr"/>
+      <c r="I9" s="28" t="inlineStr"/>
+      <c r="J9" s="28" t="inlineStr"/>
+      <c r="K9" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L9" s="28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M9" s="14" t="inlineStr"/>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr"/>
+      <c r="N9" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="25" t="inlineStr">
         <is>
           <t>Henry Mtns</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>DS6600</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F10" s="13" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G10" s="13" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
+      <c r="I10" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J10" s="13" t="inlineStr">
+      <c r="J10" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="K10" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L10" s="26" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="M10" s="14" t="inlineStr"/>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="M10" s="26" t="inlineStr"/>
+      <c r="N10" s="26" t="inlineStr">
         <is>
           <t>22.7</t>
         </is>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Kaiparowits, East</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>DS6601</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="F11" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G11" s="15" t="inlineStr">
+      <c r="G11" s="27" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J11" s="15" t="inlineStr">
+      <c r="J11" s="28" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K11" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="K11" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L11" s="28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M11" s="14" t="inlineStr"/>
-      <c r="N11" s="14" t="inlineStr">
+      <c r="M11" s="28" t="inlineStr"/>
+      <c r="N11" s="28" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>Kaiparowits, West</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="25" t="inlineStr">
         <is>
           <t>DS6603</t>
         </is>
       </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="C12" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E12" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F12" s="13" t="inlineStr">
+      <c r="F12" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
+      <c r="G12" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H12" s="13" t="inlineStr">
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
+      <c r="I12" s="26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" s="13" t="inlineStr">
+      <c r="J12" s="26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K12" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="K12" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L12" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M12" s="14" t="inlineStr"/>
-      <c r="N12" s="14" t="inlineStr">
+      <c r="M12" s="26" t="inlineStr"/>
+      <c r="N12" s="26" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>La Sal, Potash/South Cisco</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>DS6604</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G13" s="15" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J13" s="15" t="inlineStr">
+      <c r="J13" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K13" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
+      <c r="K13" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L13" s="28" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M13" s="14" t="inlineStr"/>
-      <c r="N13" s="14" t="inlineStr">
+      <c r="M13" s="28" t="inlineStr"/>
+      <c r="N13" s="28" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Pine Valley, Beaver Dam</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="25" t="inlineStr">
         <is>
           <t>DS6605</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F14" s="13" t="inlineStr">
+      <c r="F14" s="25" t="inlineStr">
         <is>
           <t>Conservation</t>
         </is>
       </c>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="G14" s="25" t="inlineStr">
         <is>
           <t>Sept 13, 2025 - Dec 31, 2025</t>
         </is>
       </c>
-      <c r="H14" s="13" t="inlineStr"/>
-      <c r="I14" s="13" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr"/>
-      <c r="K14" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L14" s="14" t="inlineStr">
+      <c r="H14" s="26" t="inlineStr"/>
+      <c r="I14" s="26" t="inlineStr"/>
+      <c r="J14" s="26" t="inlineStr"/>
+      <c r="K14" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L14" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M14" s="14" t="inlineStr"/>
-      <c r="N14" s="14" t="inlineStr">
+      <c r="M14" s="26" t="inlineStr"/>
+      <c r="N14" s="26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="27" t="inlineStr">
         <is>
           <t>San Juan, Lockhart</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>DS6606</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="27" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" s="15" t="inlineStr">
+      <c r="I15" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J15" s="15" t="inlineStr">
+      <c r="J15" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K15" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
+      <c r="K15" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L15" s="28" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="M15" s="14" t="inlineStr"/>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="M15" s="28" t="inlineStr"/>
+      <c r="N15" s="28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>San Juan, South</t>
         </is>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>DS6607</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F16" s="13" t="inlineStr">
+      <c r="F16" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="G16" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
+      <c r="I16" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J16" s="13" t="inlineStr">
+      <c r="J16" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="K16" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L16" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M16" s="14" t="inlineStr"/>
-      <c r="N16" s="14" t="inlineStr">
+      <c r="M16" s="26" t="inlineStr"/>
+      <c r="N16" s="26" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>San Rafael, Dirty Devil</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>DS6608</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="C17" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D17" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G17" s="15" t="inlineStr">
+      <c r="G17" s="27" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I17" s="15" t="inlineStr">
+      <c r="I17" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J17" s="15" t="inlineStr">
+      <c r="J17" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K17" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="K17" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L17" s="28" t="inlineStr">
         <is>
           <t>85.7</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr"/>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="M17" s="28" t="inlineStr"/>
+      <c r="N17" s="28" t="inlineStr">
         <is>
           <t>11.1</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>San Rafael, North</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>DS6609</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F18" s="13" t="inlineStr">
+      <c r="F18" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="G18" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J18" s="13" t="inlineStr">
+      <c r="J18" s="26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K18" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L18" s="14" t="inlineStr">
+      <c r="K18" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L18" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M18" s="14" t="inlineStr"/>
-      <c r="N18" s="14" t="inlineStr">
+      <c r="M18" s="26" t="inlineStr"/>
+      <c r="N18" s="26" t="inlineStr">
         <is>
           <t>10.1</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>San Rafael, South</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>DS6610</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="F19" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G19" s="15" t="inlineStr">
+      <c r="G19" s="27" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I19" s="15" t="inlineStr">
+      <c r="I19" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J19" s="15" t="inlineStr">
+      <c r="J19" s="28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K19" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L19" s="14" t="inlineStr">
+      <c r="K19" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L19" s="28" t="inlineStr">
         <is>
           <t>91.7</t>
         </is>
       </c>
-      <c r="M19" s="14" t="inlineStr"/>
-      <c r="N19" s="14" t="inlineStr">
+      <c r="M19" s="28" t="inlineStr"/>
+      <c r="N19" s="28" t="inlineStr">
         <is>
           <t>11.2</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Zion</t>
         </is>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>DS6611</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F20" s="13" t="inlineStr">
+      <c r="F20" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G20" s="13" t="inlineStr">
+      <c r="G20" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H20" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I20" s="13" t="inlineStr">
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J20" s="13" t="inlineStr">
+      <c r="J20" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K20" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L20" s="14" t="inlineStr">
+      <c r="K20" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L20" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M20" s="14" t="inlineStr"/>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="M20" s="26" t="inlineStr"/>
+      <c r="N20" s="26" t="inlineStr">
         <is>
           <t>20.7</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="27" t="inlineStr">
         <is>
           <t>Pine Valley, Virgin River</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>DS6620</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F21" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G21" s="15" t="inlineStr">
+      <c r="G21" s="27" t="inlineStr">
         <is>
           <t>Oct 24 2026 - Dec 25 2026</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I21" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J21" s="15" t="inlineStr">
+      <c r="J21" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K21" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L21" s="14" t="inlineStr">
+      <c r="K21" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L21" s="28" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="M21" s="14" t="inlineStr"/>
-      <c r="N21" s="14" t="inlineStr">
+      <c r="M21" s="28" t="inlineStr"/>
+      <c r="N21" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Pine Valley, Beaver Dam</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>DS6621</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F22" s="13" t="inlineStr">
+      <c r="F22" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="G22" s="25" t="inlineStr">
         <is>
           <t>Oct 24 2026 - Dec 25 2026</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
+      <c r="I22" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J22" s="13" t="inlineStr">
+      <c r="J22" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K22" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L22" s="14" t="inlineStr">
+      <c r="K22" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L22" s="26" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M22" s="14" t="inlineStr"/>
-      <c r="N22" s="14" t="inlineStr">
+      <c r="M22" s="26" t="inlineStr"/>
+      <c r="N22" s="26" t="inlineStr">
         <is>
           <t>11.7</t>
         </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>San Juan, North</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>DS6622</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="F23" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
+      <c r="G23" s="27" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H23" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I23" s="15" t="inlineStr">
+      <c r="I23" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J23" s="15" t="inlineStr">
+      <c r="J23" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K23" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L23" s="14" t="inlineStr">
+      <c r="K23" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L23" s="28" t="inlineStr">
         <is>
           <t>33.3</t>
         </is>
       </c>
-      <c r="M23" s="14" t="inlineStr"/>
-      <c r="N23" s="14" t="inlineStr">
+      <c r="M23" s="28" t="inlineStr"/>
+      <c r="N23" s="28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>San Juan, San Juan River</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>DS6623</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="C24" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E24" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F24" s="13" t="inlineStr">
+      <c r="F24" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G24" s="13" t="inlineStr">
+      <c r="G24" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I24" s="13" t="inlineStr">
+      <c r="I24" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J24" s="13" t="inlineStr">
+      <c r="J24" s="26" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L24" s="14" t="inlineStr">
+      <c r="K24" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L24" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M24" s="14" t="inlineStr"/>
-      <c r="N24" s="14" t="inlineStr">
+      <c r="M24" s="26" t="inlineStr"/>
+      <c r="N24" s="26" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>San Rafael, Dirty Devil</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>DS6624</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="C25" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E25" s="27" t="inlineStr">
         <is>
           <t>Archery</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="F25" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G25" s="15" t="inlineStr">
+      <c r="G25" s="27" t="inlineStr">
         <is>
           <t>Nov 11 2026 - Dec 17 2026</t>
         </is>
       </c>
-      <c r="H25" s="15" t="inlineStr">
+      <c r="H25" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I25" s="15" t="inlineStr">
+      <c r="I25" s="28" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J25" s="15" t="inlineStr">
+      <c r="J25" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L25" s="14" t="inlineStr">
+      <c r="K25" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L25" s="28" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="M25" s="14" t="inlineStr"/>
-      <c r="N25" s="14" t="inlineStr">
+      <c r="M25" s="28" t="inlineStr"/>
+      <c r="N25" s="28" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Mineral Mtns</t>
         </is>
       </c>
-      <c r="B26" s="13" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>DS6625</t>
         </is>
       </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+      <c r="C26" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E26" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F26" s="13" t="inlineStr">
+      <c r="F26" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G26" s="13" t="inlineStr">
+      <c r="G26" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H26" s="13" t="inlineStr">
+      <c r="H26" s="26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I26" s="13" t="inlineStr">
+      <c r="I26" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J26" s="13" t="inlineStr">
+      <c r="J26" s="26" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K26" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L26" s="14" t="inlineStr">
+      <c r="K26" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L26" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M26" s="14" t="inlineStr"/>
-      <c r="N26" s="14" t="inlineStr">
+      <c r="M26" s="26" t="inlineStr"/>
+      <c r="N26" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>Escalante, East</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>DS6626</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="C27" s="27" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D27" s="27" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E27" s="27" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="F27" s="27" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G27" s="15" t="inlineStr">
+      <c r="G27" s="27" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H27" s="15" t="inlineStr">
+      <c r="H27" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I27" s="15" t="inlineStr">
+      <c r="I27" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J27" s="15" t="inlineStr">
+      <c r="J27" s="28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K27" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L27" s="14" t="inlineStr">
+      <c r="K27" s="27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L27" s="28" t="inlineStr">
         <is>
           <t>71.4</t>
         </is>
       </c>
-      <c r="M27" s="14" t="inlineStr"/>
-      <c r="N27" s="14" t="inlineStr">
+      <c r="M27" s="28" t="inlineStr"/>
+      <c r="N27" s="28" t="inlineStr">
         <is>
           <t>13.4</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Escalante, West</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>DS6627</t>
         </is>
       </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>Male Only</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Desert Bighorn Sheep</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="C28" s="25" t="inlineStr">
+        <is>
+          <t>Male Only</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>Desert Bighorn Sheep</t>
+        </is>
+      </c>
+      <c r="E28" s="25" t="inlineStr">
         <is>
           <t>Any Legal Weapon</t>
         </is>
       </c>
-      <c r="F28" s="13" t="inlineStr">
+      <c r="F28" s="25" t="inlineStr">
         <is>
           <t>Once-in-a-lifetime</t>
         </is>
       </c>
-      <c r="G28" s="13" t="inlineStr">
+      <c r="G28" s="25" t="inlineStr">
         <is>
           <t>Sept 12 2026 - Nov 10 2026</t>
         </is>
       </c>
-      <c r="H28" s="13" t="inlineStr">
+      <c r="H28" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I28" s="13" t="inlineStr">
+      <c r="I28" s="26" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J28" s="13" t="inlineStr">
+      <c r="J28" s="26" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K28" s="14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="L28" s="14" t="inlineStr">
+      <c r="K28" s="25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="L28" s="26" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="M28" s="14" t="inlineStr"/>
-      <c r="N28" s="14" t="inlineStr">
+      <c r="M28" s="26" t="inlineStr"/>
+      <c r="N28" s="26" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -2249,9 +2333,9 @@
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.25" right="0.25" top="0.45" bottom="0.35" header="0.15" footer="0.15"/>
-  <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
+  <printOptions horizontalCentered="1" verticalCentered="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.35" bottom="0.35" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="1" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Georgia,Bold"&amp;12 2026 SHEEP DESERT RAM</oddHeader>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
